--- a/artfynd/A 27321-2025 artfynd.xlsx
+++ b/artfynd/A 27321-2025 artfynd.xlsx
@@ -2024,12 +2024,7 @@
         <v>74601806</v>
       </c>
       <c r="B13" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97462</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,10 +2056,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>526883.9762727764</v>
+        <v>526884</v>
       </c>
       <c r="R13" t="n">
-        <v>6367365.668482593</v>
+        <v>6367366</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2094,19 +2089,9 @@
           <t>1983-01-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">

--- a/artfynd/A 27321-2025 artfynd.xlsx
+++ b/artfynd/A 27321-2025 artfynd.xlsx
@@ -2024,7 +2024,7 @@
         <v>74601806</v>
       </c>
       <c r="B13" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27321-2025 artfynd.xlsx
+++ b/artfynd/A 27321-2025 artfynd.xlsx
@@ -2024,7 +2024,7 @@
         <v>74601806</v>
       </c>
       <c r="B13" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27321-2025 artfynd.xlsx
+++ b/artfynd/A 27321-2025 artfynd.xlsx
@@ -2024,7 +2024,7 @@
         <v>74601806</v>
       </c>
       <c r="B13" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27321-2025 artfynd.xlsx
+++ b/artfynd/A 27321-2025 artfynd.xlsx
@@ -2024,7 +2024,7 @@
         <v>74601806</v>
       </c>
       <c r="B13" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27321-2025 artfynd.xlsx
+++ b/artfynd/A 27321-2025 artfynd.xlsx
@@ -2024,7 +2024,7 @@
         <v>74601806</v>
       </c>
       <c r="B13" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27321-2025 artfynd.xlsx
+++ b/artfynd/A 27321-2025 artfynd.xlsx
@@ -2024,7 +2024,7 @@
         <v>74601806</v>
       </c>
       <c r="B13" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
